--- a/downloads/exercises/inicial-m08-i08-p01-pr01.xlsx
+++ b/downloads/exercises/inicial-m08-i08-p01-pr01.xlsx
@@ -5020,7 +5020,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>Completa indicadores con funciones ya aprendidas. Para un gráfico por categoría puedes filtrar y sumar cada categoría, sin usar funciones condicionales todavía.</x:v>
+        <x:v>Para analizar una categoría puedes aplicar un filtro y observar únicamente ese subconjunto. No necesitas calcular totales por categoría en esta actividad.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -5096,7 +5096,7 @@
         <x:v>Nota</x:v>
       </x:c>
       <x:c r="E7" s="20" t="str">
-        <x:v>Puedes obtener estos totales filtrando cada categoría y sumando los valores visibles/manuales según la práctica indicada por el profesor.</x:v>
+        <x:v>Usa los filtros para analizar subconjuntos de registros. Después borra el filtro antes de continuar con el análisis general.</x:v>
       </x:c>
       <x:c r="F7" s="20"/>
       <x:c r="G7" s="20"/>
